--- a/Minería de datos/Práctica 7/1952660_Amarillo_N1-N2_Tarea07/Parte 2/Bananya_Tablas.xlsx
+++ b/Minería de datos/Práctica 7/1952660_Amarillo_N1-N2_Tarea07/Parte 2/Bananya_Tablas.xlsx
@@ -1,27 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\10 semestre\Lab Topicos 3\1952660_Amarillo_N1-N2_Tarea07\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositories\Semestre-EneJun2026\Minería de datos\Práctica 7\1952660_Amarillo_N1-N2_Tarea07\Parte 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B517382-5225-4D36-AB1C-58E98A27A676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3EBA13B-FFD8-4595-8C10-3460EE018F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Eventos por capitulo" sheetId="1" r:id="rId1"/>
     <sheet name="Eventos por ventanas" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="35">
   <si>
     <t>Evento / Capítulo</t>
   </si>
@@ -83,16 +96,49 @@
     <t>Evento / Ventana</t>
   </si>
   <si>
-    <t>V1 (0:00-0:40)</t>
-  </si>
-  <si>
-    <t>V2 (0:41-1:20)</t>
-  </si>
-  <si>
-    <t>V3 (1:21-2:00)</t>
-  </si>
-  <si>
-    <t>V4 (2:01-final)</t>
+    <t xml:space="preserve">Support E1 = </t>
+  </si>
+  <si>
+    <t>Support E2 =</t>
+  </si>
+  <si>
+    <t>Support E3 =</t>
+  </si>
+  <si>
+    <t>Support E4 =</t>
+  </si>
+  <si>
+    <t>Support E5 =</t>
+  </si>
+  <si>
+    <t>Support E6 =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support E7 = </t>
+  </si>
+  <si>
+    <t>Cap1</t>
+  </si>
+  <si>
+    <t>Cap2</t>
+  </si>
+  <si>
+    <t>Cap3</t>
+  </si>
+  <si>
+    <t>Cap4</t>
+  </si>
+  <si>
+    <t>e1 then e2</t>
+  </si>
+  <si>
+    <t>Secuencias</t>
+  </si>
+  <si>
+    <t>Episodios</t>
+  </si>
+  <si>
+    <t>Es de Ventanas</t>
   </si>
 </sst>
 </file>
@@ -108,12 +154,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -143,9 +201,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,12 +512,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -489,7 +552,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -520,7 +583,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -541,7 +604,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -572,7 +635,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -599,7 +662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -632,7 +695,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -659,7 +722,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -701,60 +764,60 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -771,7 +834,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -786,7 +849,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -801,7 +864,7 @@
       </c>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -816,7 +879,7 @@
       </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -831,6 +894,86 @@
       </c>
       <c r="E8" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <f>COUNTIF(B2:E2, "X") / 21</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12">
+        <f t="shared" ref="B12:B17" si="0">COUNTIF(B3:E3, "X") / 21</f>
+        <v>9.5238095238095233E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>0.19047619047619047</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="D17" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
